--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומי ברק מארח את סהר כרמלי - חי קאבר</v>
+        <v>ברטין - Belki Cover</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-17</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410487&amp;sid=d14fa1900eda8196d972a3449b0a0db6</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410508&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלומי ברק מארח את סהר כרמלי - חי קאבר</v>
+        <v>ברטין - Belki Cover</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שחר לוטטי - Ginete Cover</v>
+        <v>בנימין ברון &amp; מוריאל - בן שלך מלך קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-17</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410486&amp;sid=d14fa1900eda8196d972a3449b0a0db6</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410507&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שחר לוטטי - Ginete Cover</v>
+        <v>בנימין ברון &amp; מוריאל - בן שלך מלך קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>רותם הכהן - אפר ואבק קאבר</v>
+        <v>אליאור נונה - בי נשבעתי קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-17</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410485&amp;sid=d14fa1900eda8196d972a3449b0a0db6</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410506&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>רותם הכהן - אפר ואבק קאבר</v>
+        <v>אליאור נונה - בי נשבעתי קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עידו עמדור - ביום ובלילה קאבר</v>
+        <v>אופק לוי - מהרגע הראשון קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-17</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410484&amp;sid=d14fa1900eda8196d972a3449b0a0db6</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410505&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>עידו עמדור - ביום ובלילה קאבר</v>
+        <v>אופק לוי - מהרגע הראשון קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יוסי רביב - מקלט לדמעותיי קאבר</v>
+        <v>אביב חרזי - יפה כלבנה קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-17</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410483&amp;sid=d14fa1900eda8196d972a3449b0a0db6</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410504&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,12 +621,50 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יוסי רביב - מקלט לדמעותיי קאבר</v>
+        <v>אביב חרזי - יפה כלבנה קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אביאל קוגן - מאשאפ אלייך + מצייר אותך</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410503&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אביאל קוגן - מאשאפ אלייך + מצייר אותך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ברטין - Belki Cover</v>
+        <v>אליה שטרית - לב לבן קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-17</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410508&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410516&amp;sid=c8a3f687dc532662677681ba737935f0</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-17</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ברטין - Belki Cover</v>
+        <v>אליה שטרית - לב לבן קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>בנימין ברון &amp; מוריאל - בן שלך מלך קאבר</v>
+        <v>ישראל שרביט - לב ליבי קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-04-17</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410507&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410515&amp;sid=c8a3f687dc532662677681ba737935f0</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-17</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>בנימין ברון &amp; מוריאל - בן שלך מלך קאבר</v>
+        <v>ישראל שרביט - לב ליבי קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אליאור נונה - בי נשבעתי קאבר</v>
+        <v>אבירם כהן - לב לבן קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-04-17</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410506&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410514&amp;sid=c8a3f687dc532662677681ba737935f0</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-17</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אליאור נונה - בי נשבעתי קאבר</v>
+        <v>אבירם כהן - לב לבן קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אופק לוי - מהרגע הראשון קאבר</v>
+        <v>שירה שוורץ - תקופה חרא קאבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-04-17</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410505&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410513&amp;sid=c8a3f687dc532662677681ba737935f0</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-17</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אופק לוי - מהרגע הראשון קאבר</v>
+        <v>שירה שוורץ - תקופה חרא קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אביב חרזי - יפה כלבנה קאבר</v>
+        <v>שיר אסייג - את המחר שלי קאבר</v>
       </c>
       <c r="B6" t="str">
         <v>2026-04-17</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410504&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410512&amp;sid=c8a3f687dc532662677681ba737935f0</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-17</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אביב חרזי - יפה כלבנה קאבר</v>
+        <v>שיר אסייג - את המחר שלי קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אביאל קוגן - מאשאפ אלייך + מצייר אותך</v>
+        <v>עילאי אהרוני - כשאלך קאבר</v>
       </c>
       <c r="B7" t="str">
         <v>2026-04-17</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410503&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410511&amp;sid=c8a3f687dc532662677681ba737935f0</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-17</v>
@@ -659,12 +659,88 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אביאל קוגן - מאשאפ אלייך + מצייר אותך</v>
+        <v>עילאי אהרוני - כשאלך קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ליאור כהן - השיר האחרון קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410510&amp;sid=c8a3f687dc532662677681ba737935f0</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>ליאור כהן - השיר האחרון קאבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>טליה אייזנקוט - לב לבן קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410509&amp;sid=c8a3f687dc532662677681ba737935f0</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>טליה אייזנקוט - לב לבן קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אליה שטרית - לב לבן קאבר</v>
+        <v>נאור בן דוד - תודה על הכל קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410516&amp;sid=c8a3f687dc532662677681ba737935f0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410518&amp;sid=61eedd5bd59ee327b8582a6c9bd3efd8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,278 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אליה שטרית - לב לבן קאבר</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ישראל שרביט - לב ליבי קאבר</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410515&amp;sid=c8a3f687dc532662677681ba737935f0</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>ישראל שרביט - לב ליבי קאבר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>אבירם כהן - לב לבן קאבר</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410514&amp;sid=c8a3f687dc532662677681ba737935f0</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>אבירם כהן - לב לבן קאבר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>שירה שוורץ - תקופה חרא קאבר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410513&amp;sid=c8a3f687dc532662677681ba737935f0</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>שירה שוורץ - תקופה חרא קאבר</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>שיר אסייג - את המחר שלי קאבר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410512&amp;sid=c8a3f687dc532662677681ba737935f0</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>שיר אסייג - את המחר שלי קאבר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>עילאי אהרוני - כשאלך קאבר</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410511&amp;sid=c8a3f687dc532662677681ba737935f0</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>עילאי אהרוני - כשאלך קאבר</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>ליאור כהן - השיר האחרון קאבר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410510&amp;sid=c8a3f687dc532662677681ba737935f0</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>ליאור כהן - השיר האחרון קאבר</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>טליה אייזנקוט - לב לבן קאבר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410509&amp;sid=c8a3f687dc532662677681ba737935f0</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>טליה אייזנקוט - לב לבן קאבר</v>
+        <v>נאור בן דוד - תודה על הכל קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נאור בן דוד - תודה על הכל קאבר</v>
+        <v>ליאור מזרחי - מקלט לדמעותיי קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410518&amp;sid=61eedd5bd59ee327b8582a6c9bd3efd8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410539&amp;sid=2ed35c4ba0b7bddf7b481a8419bf43c4</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,12 +469,50 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נאור בן דוד - תודה על הכל קאבר</v>
+        <v>ליאור מזרחי - מקלט לדמעותיי קאבר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>איתי עמר - אהובתי קאבר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410533&amp;sid=2ed35c4ba0b7bddf7b481a8419bf43c4</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>איתי עמר - אהובתי קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליאור מזרחי - מקלט לדמעותיי קאבר</v>
+        <v>עומרי פרחן - גיבורים קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-21</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410539&amp;sid=2ed35c4ba0b7bddf7b481a8419bf43c4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410561&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליאור מזרחי - מקלט לדמעותיי קאבר</v>
+        <v>עומרי פרחן - גיבורים קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>איתי עמר - אהובתי קאבר</v>
+        <v>יהב חדד - החול יזכור קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-21</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410533&amp;sid=2ed35c4ba0b7bddf7b481a8419bf43c4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410560&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,12 +507,240 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>איתי עמר - אהובתי קאבר</v>
+        <v>יהב חדד - החול יזכור קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>בן ימין - את ההוכחה שיש אלוהים קאבר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410559&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>בן ימין - את ההוכחה שיש אלוהים קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>אילאי גואריהן - המכתב האחרון קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410558&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>אילאי גואריהן - המכתב האחרון קאבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>אילאי ברדה - כאב של לוחמים קאבר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410557&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אילאי ברדה - כאב של לוחמים קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אבישי לוי - כאב של לוחמים קאבר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410556&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אבישי לוי - כאב של לוחמים קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אבירם ברמי &amp; יובל בדלין - כל החיילים חוזרים הביתה קאבר הורדה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410555&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אבירם ברמי &amp; יובל בדלין - כל החיילים חוזרים הביתה קאבר הורדה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אבירם ברמי - ארץ צבי קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410554&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אבירם ברמי - ארץ צבי קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>